--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Records self-reported daily portions of fruit based on ATHIS 2025 question DH2. Applicable only for respondents who eat fruit daily (DH1 = 'Täglich oder mehrmals täglich'). Observation code: LOINC 89765-5 'Servings of fruit per day [PhenX]'.</t>
+    <t>Records self-reported daily portions of fruit based on ATHIS 2025 question DH2. Applicable only for respondents who eat fruit daily (DH1 = 'Täglich oder mehrmals täglich'). Observation code: LOINC 80457-5 'Fruit servings 24 hour Estimated'.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -855,8 +855,8 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="89765-5"/&gt;
-    &lt;display value="Servings of fruit per day [PhenX]"/&gt;
+    &lt;code value="80457-5"/&gt;
+    &lt;display value="Fruit servings 24 hour Estimated"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}nutrition-fruit-portions-range:Fruit portions per day must be between 1 and 99. {value.ofType(Quantity).value &gt;= 1 and value.ofType(Quantity).value &lt;= 99}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}nutrition-fruit-portions-range:Fruit portions per day must be between 1 and 99. {value.empty() or (value.ofType(Quantity).value &gt;= 1 and value.ofType(Quantity).value &lt;= 99)}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1252,7 +1252,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the result is missing</t>
+    <t>Reason why no clinically or analytically meaningful result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
@@ -1729,7 +1729,7 @@
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the component result is missing</t>
+    <t>Reason why no clinically or analytically meaningful component result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -6829,7 +6829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>395</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -9841,7 +9841,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>546</v>
       </c>
@@ -9860,7 +9860,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-nutrition-fruitportions-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
